--- a/output/pdf_financials_xlsx/ORNG.xlsx
+++ b/output/pdf_financials_xlsx/ORNG.xlsx
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.628733</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.934532</v>
       </c>
     </row>
     <row r="93">
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.00165</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.196872</v>
       </c>
     </row>
     <row r="104">
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.11849</v>
+        <v>0.11684</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>1.164426</v>
+        <v>0.967554</v>
       </c>
     </row>
     <row r="107">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000495</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.042611</v>
+        <v>0.000495</v>
       </c>
     </row>
     <row r="119">
@@ -2610,7 +2610,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.628733</v>
       </c>
@@ -2964,7 +2968,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>-0.00165</v>
       </c>
@@ -3044,7 +3052,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>-0.000495</v>
       </c>

--- a/output/pdf_financials_xlsx/ORNG.xlsx
+++ b/output/pdf_financials_xlsx/ORNG.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.1345</v>
+        <v>0.182084</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.7992860000000001</v>
+        <v>4.293183</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.1345</v>
+        <v>-0.182084</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.7992860000000001</v>
+        <v>-4.293183</v>
       </c>
     </row>
     <row r="12">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.034514</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.130006</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.034514</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.130006</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.036164</v>
+        <v>0.00165</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.328528</v>
+        <v>0.198522</v>
       </c>
     </row>
     <row r="49">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3768,14 +3768,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>-0.182084</v>
+        <v>0.182084</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>-4.293183</v>
+        <v>4.293183</v>
       </c>
     </row>
     <row r="57">

--- a/output/pdf_financials_xlsx/ORNG.xlsx
+++ b/output/pdf_financials_xlsx/ORNG.xlsx
@@ -517,7 +517,7 @@
         <v>0.1345</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.7992860000000001</v>
+        <v>0.810536</v>
       </c>
     </row>
     <row r="8">
@@ -3520,7 +3520,11 @@
           <t>Director fees (Note 9)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
